--- a/docs/AWS構成検討まとめ.xlsx
+++ b/docs/AWS構成検討まとめ.xlsx
@@ -13,13 +13,14 @@
     <sheet sheetId="7" name="典型的なアーキテクチャ構成" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="AWS向け_オンプレ比較" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="学習の進め方" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="料金の目安" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="240">
   <si>
     <t>AWS構成検討まとめ</t>
   </si>
@@ -651,12 +652,171 @@
   <si>
     <t>体系的に学ぶなら「AWS認定 クラウドプラクティショナー」「AWS認定 デベロッパー」等の学習教材も活用する</t>
   </si>
+  <si>
+    <t>料金の目安（学習規模での試算）</t>
+  </si>
+  <si>
+    <t>EC2／RDS／Elastic Beanstalk／CloudWatchを使った学習・検証（beautyPOSのAWS化）にかかる費用の目安</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF2F4A66"/>
+        <sz val="11"/>
+        <rFont val="Yu Gothic"/>
+      </rPr>
+      <t xml:space="preserve">💰 結論：実質ほぼ0円で収まる見込み
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="333333"/>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+      </rPr>
+      <t>2025年7月15日以降に作成した新規AWSアカウントは、サインアップ時に$100（オンボーディング完了で最大$200）のクレジットが自動付与され、最初の6ヶ月間の利用料に自動的に充当される。今回の学習規模（小規模インスタンスを断続稼働）なら、このクレジット内で確実に収まる。</t>
+    </r>
+  </si>
+  <si>
+    <t>■ クレジットを使わなかった場合の概算（実際の料金水準の目安）</t>
+  </si>
+  <si>
+    <t>リソース</t>
+  </si>
+  <si>
+    <t>料金目安</t>
+  </si>
+  <si>
+    <t>18日間フル稼働した場合</t>
+  </si>
+  <si>
+    <t>EC2（t3.micro）</t>
+  </si>
+  <si>
+    <t>$0.0104／時間</t>
+  </si>
+  <si>
+    <t>約$4.5（≒700円）</t>
+  </si>
+  <si>
+    <t>使わない時間は停止すればさらに安くなる</t>
+  </si>
+  <si>
+    <t>RDS（db.t3.micro, PostgreSQL）</t>
+  </si>
+  <si>
+    <t>$0.018／時間</t>
+  </si>
+  <si>
+    <t>約$4.3（≒650円）</t>
+  </si>
+  <si>
+    <t>ストレージ20GBまでは無料枠内</t>
+  </si>
+  <si>
+    <t>Elastic Beanstalk本体</t>
+  </si>
+  <si>
+    <t>無料</t>
+  </si>
+  <si>
+    <t>¥0</t>
+  </si>
+  <si>
+    <t>裏側のEC2／RDS分のみ課金される</t>
+  </si>
+  <si>
+    <t>CloudWatch（ログ5GB・アラーム10件まで）</t>
+  </si>
+  <si>
+    <t>無料枠内</t>
+  </si>
+  <si>
+    <t>このスケール感なら十分収まる</t>
+  </si>
+  <si>
+    <t>合計（フル稼働・クレジット未使用の場合）：約$9〜10（≒1,400〜1,500円）　／　作業時だけ起動し使わない時間は停止すれば、この半分以下（数百円相当）で収まる</t>
+  </si>
+  <si>
+    <t>■ ⚠️ 唯一注意したい点：Elastic Beanstalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「ロードバランス環境」で作成すると Application Load Balancer（ALB）が自動作成され、これだけは無料利用枠の対象外（$0.0225／時間＋処理量課金）。
+学習目的なら「単一インスタンス環境（Single instance）」を選べばALBが作られず無料枠内に収まる。</t>
+  </si>
+  <si>
+    <t>■ 忘れると危険なこと</t>
+  </si>
+  <si>
+    <t>・クレジットカード登録は必須（課金されなくても登録は必要）</t>
+  </si>
+  <si>
+    <t>・学習終了後にEC2・RDS・Beanstalk環境を削除／停止するのを忘れないこと（放置すると6ヶ月のクレジット期限後や、規模が大きくなった際に課金が発生）</t>
+  </si>
+  <si>
+    <t>・RDSは「停止」しても最大7日で自動再起動する仕様なので、使わないなら完全に削除するのが安全</t>
+  </si>
+  <si>
+    <t>■ 参照情報</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+      </rPr>
+      <t xml:space="preserve">・AWS Free Tierの仕組み　</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="888888"/>
+        <sz val="9.5"/>
+        <rFont val="Yu Gothic"/>
+      </rPr>
+      <t>https://aws.amazon.com/free/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+      </rPr>
+      <t xml:space="preserve">・Elastic Load Balancing料金　</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="888888"/>
+        <sz val="9.5"/>
+        <rFont val="Yu Gothic"/>
+      </rPr>
+      <t>https://aws.amazon.com/elasticloadbalancing/pricing/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+      </rPr>
+      <t xml:space="preserve">・Amazon CloudWatch料金　</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="888888"/>
+        <sz val="9.5"/>
+        <rFont val="Yu Gothic"/>
+      </rPr>
+      <t>https://aws.amazon.com/cloudwatch/pricing/</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -672,16 +832,16 @@
     </font>
     <font>
       <color rgb="FF5A6472"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
     <font>
       <b/>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
     <font>
@@ -693,6 +853,21 @@
     <font>
       <b/>
       <color rgb="FF3E5E82"/>
+      <sz val="10"/>
+      <name val="Yu Gothic"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2F4A66"/>
+      <sz val="10"/>
+      <name val="Yu Gothic"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Yu Gothic"/>
+    </font>
+    <font>
+      <color rgb="FF5A6472"/>
       <sz val="10.5"/>
       <name val="Yu Gothic"/>
     </font>
@@ -703,11 +878,11 @@
       <name val="Yu Gothic"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <name val="Yu Gothic"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -734,8 +909,13 @@
         <fgColor rgb="FFF5F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFD0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -758,11 +938,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDBB77"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDBB77"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDDBB77"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDDBB77"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -798,6 +993,33 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1298,6 +1520,230 @@
     <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="4" ht="65" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" ht="50" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:D25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
@@ -1475,7 +1921,7 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1599,7 +2045,7 @@
     <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1709,7 +2155,7 @@
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1809,7 +2255,7 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1898,7 +2344,7 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2082,7 +2528,7 @@
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2208,7 +2654,7 @@
     <mergeCell ref="A13:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2330,6 +2776,6 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>